--- a/artfynd/A 17535-2024 artfynd.xlsx
+++ b/artfynd/A 17535-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16998469</v>
+        <v>16998495</v>
       </c>
       <c r="B2" t="n">
-        <v>101219</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221978</v>
+        <v>1879</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bergjohannesört</t>
+          <t>Trollsmultron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypericum montanum</t>
+          <t>Drymocallis rupestris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soják</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>356866.4408801338</v>
+        <v>356812</v>
       </c>
       <c r="R2" t="n">
-        <v>6525414.198274841</v>
+        <v>6525470</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2014-06-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-06-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16998470</v>
+        <v>16998472</v>
       </c>
       <c r="B3" t="n">
-        <v>108203</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219716</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Krusfrö</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Selinum carvifolia</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) L.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>356871.8955254279</v>
+        <v>356866</v>
       </c>
       <c r="R3" t="n">
-        <v>6525295.37759672</v>
+        <v>6525464</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +850,9 @@
           <t>2014-06-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-06-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -916,6 +886,648 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>16998470</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111399</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219716</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Krusfrö</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Selinum carvifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Säljebyn NV, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>356872</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6525295</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ånimskog</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Pro-Natura / Lst VGL</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Tallskog med gran- och lövinslag, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anita Stridvall, Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16998498</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108201</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Säljebyn NV, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>356812</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6525470</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ånimskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Pro-Natura / Lst VGL</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Tallskog med gran- och lövinslag, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anita Stridvall, Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16998471</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102225</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221223</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vippärt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lathyrus niger</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Säljebyn NV, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>356822</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6525474</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ånimskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Pro-Natura / Lst VGL</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Tallskog med gran- och lövinslag, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anita Stridvall, Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>16998469</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103647</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221978</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bergjohannesört</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hypericum montanum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Säljebyn NV, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>356866</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6525414</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ånimskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Pro-Natura / Lst VGL</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Tallskog med gran- och lövinslag, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anita Stridvall, Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>16998474</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Säljebyn NV, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>356861</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6525466</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ånimskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Pro-Natura / Lst VGL</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Tallskog med gran- och lövinslag, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anita Stridvall, Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>16998502</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Säljebyn NV, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>356812</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6525470</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ånimskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2014-06-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Pro-Natura / Lst VGL</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Tallskog med gran- och lövinslag, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anita Stridvall, Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
